--- a/artfynd/A 15971-2026 artfynd.xlsx
+++ b/artfynd/A 15971-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132534327</v>
+        <v>132525980</v>
       </c>
       <c r="B2" t="n">
-        <v>99130</v>
+        <v>91974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582587</v>
+        <v>582808</v>
       </c>
       <c r="R2" t="n">
-        <v>7043485</v>
+        <v>7043666</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132525980</v>
+        <v>132534952</v>
       </c>
       <c r="B3" t="n">
-        <v>91918</v>
+        <v>91974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -826,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582808</v>
+        <v>582767</v>
       </c>
       <c r="R3" t="n">
-        <v>7043666</v>
+        <v>7043878</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132525197</v>
+        <v>132526440</v>
       </c>
       <c r="B4" t="n">
-        <v>57958</v>
+        <v>92406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,39 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>582828</v>
+        <v>582854</v>
       </c>
       <c r="R4" t="n">
-        <v>7043790</v>
+        <v>7043666</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -973,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -983,12 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,53 +996,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132525548</v>
+        <v>132525094</v>
       </c>
       <c r="B5" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>582773</v>
+        <v>582850</v>
       </c>
       <c r="R5" t="n">
-        <v>7043726</v>
+        <v>7043795</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1090,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,12 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:22</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,44 +1091,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132534661</v>
+        <v>132525979</v>
       </c>
       <c r="B6" t="n">
-        <v>80438</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582746</v>
+        <v>582794</v>
       </c>
       <c r="R6" t="n">
-        <v>7043620</v>
+        <v>7043687</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1202,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,11 +1213,11 @@
         <v>132526091</v>
       </c>
       <c r="B7" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1346,57 +1317,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132534520</v>
+        <v>132525951</v>
       </c>
       <c r="B8" t="n">
-        <v>99130</v>
+        <v>80488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>582675</v>
+        <v>582796</v>
       </c>
       <c r="R8" t="n">
-        <v>7043532</v>
+        <v>7043677</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1425,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1435,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1450,64 +1412,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132918629</v>
+        <v>132534661</v>
       </c>
       <c r="B9" t="n">
-        <v>99140</v>
+        <v>80488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sundmoberget, Sundmoberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>582607</v>
+        <v>582746</v>
       </c>
       <c r="R9" t="n">
-        <v>7043747</v>
+        <v>7043620</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1531,22 +1489,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1561,15 +1519,922 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132918313</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>582793</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7043564</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132526109</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>582807</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7043675</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132525197</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>582828</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7043790</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132525548</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>582773</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7043726</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132525807</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>582765</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7043695</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
           <t>Kim Hultgren</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX14" t="inlineStr">
         <is>
           <t>Kim Hultgren</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132534327</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>582587</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7043485</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132534520</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>582675</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7043532</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132918629</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sundmoberget, Sundmoberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>582607</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7043747</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15971-2026 artfynd.xlsx
+++ b/artfynd/A 15971-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132525980</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132534952</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132526440</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132525094</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132525979</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132526091</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132525951</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132534661</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132918313</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1747,6 +1797,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132526109</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1864,6 +1919,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132525197</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1981,6 +2041,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132525548</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2092,6 +2157,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132525807</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2208,6 +2278,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132534327</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2324,6 +2399,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132534520</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2435,8 +2515,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132918629</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>